--- a/practice-files/day10-VLOOKUP.xlsx
+++ b/practice-files/day10-VLOOKUP.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用户表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -893,19 +892,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -963,15 +949,15 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>800.79</v>
+        <v>889.78</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
@@ -986,15 +972,15 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1214.28</v>
+        <v>1422.16</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -1009,15 +995,15 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1292.2</v>
+        <v>1730.44</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -1032,15 +1018,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>538.73</v>
+        <v>946.52</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -1059,11 +1045,11 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1459.32</v>
+        <v>1172.73</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1078,15 +1064,15 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>U1003</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1203.13</v>
+        <v>864.5</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1101,15 +1087,15 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1584.58</v>
+        <v>1934.09</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1124,15 +1110,15 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1262.88</v>
+        <v>947.1900000000001</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1147,15 +1133,15 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1359.5</v>
+        <v>1696.74</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -1170,15 +1156,15 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>866.0599999999999</v>
+        <v>830.88</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1193,15 +1179,15 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>532.21</v>
+        <v>1504.32</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -1216,15 +1202,15 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>802.75</v>
+        <v>198.94</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1239,15 +1225,15 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>707.0599999999999</v>
+        <v>428.11</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -1262,15 +1248,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>569.49</v>
+        <v>1918.54</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -1285,15 +1271,15 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1570.83</v>
+        <v>335.57</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -1308,15 +1294,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1726.26</v>
+        <v>348.1</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -1331,15 +1317,15 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>529.12</v>
+        <v>1013.53</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -1354,15 +1340,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1833.88</v>
+        <v>1303.83</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -1377,15 +1363,15 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1044.86</v>
+        <v>666.47</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -1400,15 +1386,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>542.11</v>
+        <v>912.3099999999999</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -1423,15 +1409,15 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>589.1799999999999</v>
+        <v>1203.27</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -1446,15 +1432,15 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>881.0700000000001</v>
+        <v>655.3</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -1469,15 +1455,15 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1419.27</v>
+        <v>769.04</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -1492,15 +1478,15 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>435.03</v>
+        <v>1735.29</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -1515,15 +1501,15 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>600.6799999999999</v>
+        <v>1038.78</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>

--- a/practice-files/day10-VLOOKUP.xlsx
+++ b/practice-files/day10-VLOOKUP.xlsx
@@ -571,7 +571,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>【注意】VLOOKUP只能从左往右查。如果想"根据姓名查ID"（从右往左），需要用INDEX+MATCH或XLOOKUP。</t>
+          <t>【注意】VLOOKUP只能从左往右查。如果想"根据姓名查ID"（从右往左），需要用INDEX+MATCH或XLOOKUP（XLOOKUP需Excel 2021/365或WPS 2021以上版本）。</t>
         </is>
       </c>
     </row>
@@ -953,11 +953,11 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>889.78</v>
+        <v>1726.23</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
@@ -972,15 +972,15 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1422.16</v>
+        <v>1851.63</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
@@ -995,15 +995,15 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1730.44</v>
+        <v>1111.9</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
@@ -1018,15 +1018,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>946.52</v>
+        <v>189.25</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -1041,15 +1041,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1172.73</v>
+        <v>1210.34</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1064,15 +1064,15 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>864.5</v>
+        <v>963.96</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1087,15 +1087,15 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1934.09</v>
+        <v>1888.22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1110,15 +1110,15 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>947.1900000000001</v>
+        <v>1216.17</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1133,15 +1133,15 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1006</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1696.74</v>
+        <v>1227.24</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -1156,15 +1156,15 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>830.88</v>
+        <v>1925.73</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1179,15 +1179,15 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1504.32</v>
+        <v>1651.77</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>198.94</v>
+        <v>967.48</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -1225,15 +1225,15 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>428.11</v>
+        <v>1994.04</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -1248,15 +1248,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1918.54</v>
+        <v>1939.66</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -1271,15 +1271,15 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>335.57</v>
+        <v>699.95</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -1294,15 +1294,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>348.1</v>
+        <v>693.12</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -1321,11 +1321,11 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1013.53</v>
+        <v>1893.13</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -1340,15 +1340,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1303.83</v>
+        <v>663.3099999999999</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -1363,15 +1363,15 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>666.47</v>
+        <v>1736.58</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -1386,15 +1386,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>912.3099999999999</v>
+        <v>950.85</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -1409,15 +1409,15 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1203.27</v>
+        <v>755.47</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -1432,15 +1432,15 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>655.3</v>
+        <v>1531.98</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -1455,15 +1455,15 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>769.04</v>
+        <v>305.48</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -1478,15 +1478,15 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1735.29</v>
+        <v>995.1900000000001</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -1505,11 +1505,11 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1038.78</v>
+        <v>1608.66</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>

--- a/practice-files/day10-VLOOKUP.xlsx
+++ b/practice-files/day10-VLOOKUP.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -87,16 +103,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -572,6 +593,41 @@
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>【注意】VLOOKUP只能从左往右查。如果想"根据姓名查ID"（从右往左），需要用INDEX+MATCH或XLOOKUP（XLOOKUP需Excel 2021/365或WPS 2021以上版本）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: VLOOKUP第四参数TRUE和FALSE各适合什么场景？</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" hidden="1" outlineLevel="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: FALSE=精确匹配，找ID必须用它（找不到返回#N/A）；TRUE=近似匹配，"找最接近且不超过"，适合金额→折扣档位，但要求查找列升序。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: 两张表都有"用户ID"，VLOOKUP却返回#N/A，最可能的原因？</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" hidden="1" outlineLevel="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 格式不一致——一边是文本一边是数字（看对齐方式分辨），或有多余空格。先统一两边格式再匹配。</t>
         </is>
       </c>
     </row>
@@ -596,286 +652,286 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>用户姓名</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>城市</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>U1001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>金牌</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>U1002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>银牌</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>U1003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>铜牌</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>U1004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>赵六</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>金牌</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>U1005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>孙七</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>银牌</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>U1006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>周八</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>铜牌</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>成都</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>U1007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>吴九</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>金牌</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>武汉</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>U1008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>郑十</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>银牌</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>南京</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>U1009</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>钱十一</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>铜牌</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>U1010</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>冯十二</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>金牌</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>U1011</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>陈十三</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>银牌</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>广州</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>U1012</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>褚十四</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>铜牌</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
@@ -905,616 +961,616 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>订单ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>用户ID</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>用户姓名（VLOOKUP）</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>等级（VLOOKUP）</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>城市（VLOOKUP）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>ORD-0001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>U1012</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>1726.23</v>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="C2" s="7" t="n">
+        <v>889.78</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr"/>
+      <c r="G2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ORD-0002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>U1004</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1851.63</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1422.16</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>U1007</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>1730.44</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>946.52</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1172.73</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>864.5</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1934.09</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>U1010</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>947.1900000000001</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>U1007</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1696.74</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0003</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>U1010</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>830.88</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>U1005</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1504.32</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>U1003</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>198.94</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>428.11</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>U1012</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1918.54</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>U1002</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1111.9</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0004</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>U1003</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>189.25</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0005</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C16" s="7" t="n">
+        <v>335.57</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>U1010</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>1013.53</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>U1010</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1303.83</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>666.47</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>U1008</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>912.3099999999999</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>U1005</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>1210.34</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0006</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="C22" s="7" t="n">
+        <v>1203.27</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>U1002</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>963.96</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0007</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>U1007</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1888.22</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0008</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>U1002</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1216.17</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0009</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>U1006</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1227.24</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0010</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>U1004</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1925.73</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0011</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="C23" s="7" t="n">
+        <v>655.3</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>769.04</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>ORD-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>U1011</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>1651.77</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0012</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>U1003</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>967.48</v>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0013</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>U1003</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1994.04</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0014</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>U1008</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1939.66</v>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0015</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>U1007</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>699.95</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0016</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>U1003</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>693.12</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0017</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>U1011</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1893.13</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0018</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>U1002</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>663.3099999999999</v>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0019</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>U1007</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>1736.58</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-22</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0020</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>U1009</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>950.85</v>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0021</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>U1009</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>755.47</v>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0022</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>U1008</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1531.98</v>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0023</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>U1009</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>305.48</v>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>ORD-0024</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>U1012</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>995.1900000000001</v>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="C25" s="7" t="n">
+        <v>1735.29</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>ORD-0025</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>U1010</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
-        <v>1608.66</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
+      <c r="C26" s="7" t="n">
+        <v>1038.78</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/practice-files/day10-VLOOKUP.xlsx
+++ b/practice-files/day10-VLOOKUP.xlsx
@@ -599,7 +599,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
     <row r="22" hidden="1" outlineLevel="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: FALSE=精确匹配，找ID必须用它（找不到返回#N/A）；TRUE=近似匹配，"找最接近且不超过"，适合金额→折扣档位，但要求查找列升序。</t>
+          <t>答案: FALSE=精确匹配，找ID必须用它（找不到返回#N/A）；TRUE=近似匹配，"找最接近且不超过"，适合金额→折扣档位，但要求查找列升序。</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
     <row r="25" hidden="1" outlineLevel="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 格式不一致——一边是文本一边是数字（看对齐方式分辨），或有多余空格。先统一两边格式再匹配。</t>
+          <t>答案: 格式不一致——一边是文本一边是数字（看对齐方式分辨），或有多余空格。先统一两边格式再匹配。</t>
         </is>
       </c>
     </row>

--- a/practice-files/day10-VLOOKUP.xlsx
+++ b/practice-files/day10-VLOOKUP.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用户表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="订单表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动参与名单(备用实战)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -587,45 +588,52 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>【备用实战】"活动参与名单(备用实战)"工作表的用户ID与"用户表"对齐，直接VLOOKUP练匹配用户等级</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>【注意】VLOOKUP只能从左往右查。如果想"根据姓名查ID"（从右往左），需要用INDEX+MATCH或XLOOKUP（XLOOKUP需Excel 2021/365或WPS 2021以上版本）。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>思考题1: VLOOKUP第四参数TRUE和FALSE各适合什么场景？</t>
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" outlineLevel="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" hidden="1" outlineLevel="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>答案: FALSE=精确匹配，找ID必须用它（找不到返回#N/A）；TRUE=近似匹配，"找最接近且不超过"，适合金额→折扣档位，但要求查找列升序。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>思考题2: 两张表都有"用户ID"，VLOOKUP却返回#N/A，最可能的原因？</t>
         </is>
       </c>
     </row>
-    <row r="25" hidden="1" outlineLevel="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26" hidden="1" outlineLevel="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>答案: 格式不一致——一边是文本一边是数字（看对齐方式分辨），或有多余空格。先统一两边格式再匹配。</t>
         </is>
@@ -1005,15 +1013,15 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>889.78</v>
+        <v>1047.59</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -1028,15 +1036,15 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>1422.16</v>
+        <v>1580.28</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -1051,15 +1059,15 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1730.44</v>
+        <v>439.51</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -1074,15 +1082,15 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>946.52</v>
+        <v>1947.58</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr"/>
@@ -1097,15 +1105,15 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1172.73</v>
+        <v>625.9299999999999</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -1120,15 +1128,15 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>864.5</v>
+        <v>1825.2</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
@@ -1143,15 +1151,15 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1934.09</v>
+        <v>55.34</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -1170,11 +1178,11 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>947.1900000000001</v>
+        <v>1354.59</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr"/>
@@ -1189,15 +1197,15 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>1696.74</v>
+        <v>196.34</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -1212,15 +1220,15 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>830.88</v>
+        <v>500.76</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
@@ -1235,15 +1243,15 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1504.32</v>
+        <v>147.66</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -1258,15 +1266,15 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>U1003</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>198.94</v>
+        <v>1711.88</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr"/>
@@ -1281,15 +1289,15 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>428.11</v>
+        <v>659.78</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -1304,15 +1312,15 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1918.54</v>
+        <v>68.86</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -1327,15 +1335,15 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>335.57</v>
+        <v>382.5</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1354,11 +1362,11 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>348.1</v>
+        <v>573.2</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -1373,15 +1381,15 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1006</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1013.53</v>
+        <v>406.6</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1396,15 +1404,15 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>1303.83</v>
+        <v>580.0700000000001</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1419,15 +1427,15 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>666.47</v>
+        <v>1609.8</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -1442,15 +1450,15 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>912.3099999999999</v>
+        <v>1407.53</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
@@ -1465,15 +1473,15 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1203.27</v>
+        <v>252.24</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr"/>
@@ -1488,15 +1496,15 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>655.3</v>
+        <v>1372.87</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
@@ -1511,15 +1519,15 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>769.04</v>
+        <v>1569.37</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr"/>
@@ -1538,11 +1546,11 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>1735.29</v>
+        <v>1765.9</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
@@ -1557,20 +1565,700 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1038.78</v>
+        <v>270.23</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>昵称</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>参与活动</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>参与日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>柠檬茶</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>双11狂欢</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>U1012</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>月亮</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>618年中庆</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>月亮</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>大树</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>柚子</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>北岛</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>U1008</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>北岛</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>海盐</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>双11狂欢</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>夏夜</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>柠檬茶</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>U1010</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>山川</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>夜风</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>U1007</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>白鹿</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>U1002</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>石头</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>星星</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>阿明</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>618年中庆</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>U1008</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>海盐</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>U1002</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>大树</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>浮云</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>U1002</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>阿明</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>U1012</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>白鹿</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>星星</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>U1008</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>星星</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>U1007</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>阿明</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>星星</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>星星</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>U1012</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>白鹿</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>U1002</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>大树</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/practice-files/day10-VLOOKUP.xlsx
+++ b/practice-files/day10-VLOOKUP.xlsx
@@ -1013,15 +1013,15 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>1047.59</v>
+        <v>1333.99</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
@@ -1036,15 +1036,15 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>1580.28</v>
+        <v>1084.21</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -1059,15 +1059,15 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>439.51</v>
+        <v>1685.69</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr"/>
@@ -1082,15 +1082,15 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1947.58</v>
+        <v>1399.04</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr"/>
@@ -1105,15 +1105,15 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>625.9299999999999</v>
+        <v>251.93</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr"/>
@@ -1128,15 +1128,15 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1825.2</v>
+        <v>866.4</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
@@ -1151,15 +1151,15 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>55.34</v>
+        <v>1929.01</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr"/>
@@ -1174,15 +1174,15 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>1354.59</v>
+        <v>319.45</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr"/>
@@ -1197,15 +1197,15 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>196.34</v>
+        <v>1118.22</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr"/>
@@ -1220,15 +1220,15 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>500.76</v>
+        <v>1874.25</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
@@ -1243,15 +1243,15 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>147.66</v>
+        <v>1267.13</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
@@ -1266,15 +1266,15 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1006</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1711.88</v>
+        <v>1846.32</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr"/>
@@ -1293,11 +1293,11 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>659.78</v>
+        <v>1951.6</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr"/>
@@ -1312,15 +1312,15 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>68.86</v>
+        <v>1403.91</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -1335,15 +1335,15 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>382.5</v>
+        <v>1533.51</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>573.2</v>
+        <v>1888.21</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr"/>
@@ -1381,15 +1381,15 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>406.6</v>
+        <v>1793.04</v>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1404,15 +1404,15 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>580.0700000000001</v>
+        <v>1626.19</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1427,15 +1427,15 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1609.8</v>
+        <v>333.39</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr"/>
@@ -1450,15 +1450,15 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>U1003</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1407.53</v>
+        <v>1512.86</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr"/>
@@ -1473,15 +1473,15 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>U1003</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>252.24</v>
+        <v>538.59</v>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr"/>
@@ -1496,15 +1496,15 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>1372.87</v>
+        <v>447.8</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
@@ -1519,15 +1519,15 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1569.37</v>
+        <v>249.84</v>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr"/>
@@ -1546,11 +1546,11 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>1765.9</v>
+        <v>1144.48</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
@@ -1565,15 +1565,15 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>270.23</v>
+        <v>610.9</v>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr"/>
@@ -1625,110 +1625,110 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>柠檬茶</t>
+          <t>白鹿</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>双11狂欢</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>小鱼</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>618年中庆</t>
+          <t>元旦集卡</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>山川</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>大树</t>
+          <t>奶茶</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>柚子</t>
+          <t>星星</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>520告白季</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -1740,51 +1740,51 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>北岛</t>
+          <t>柠檬茶</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>520告白季</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-03-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>北岛</t>
+          <t>夜风</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-01-14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>海盐</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1794,51 +1794,51 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>夏夜</t>
+          <t>麦子</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>柠檬茶</t>
+          <t>青柠</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
@@ -1850,83 +1850,83 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>山川</t>
+          <t>阿明</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>夜风</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>白鹿</t>
+          <t>海盐</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>端午打卡</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>石头</t>
+          <t>柠檬茶</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-14</t>
         </is>
       </c>
     </row>
@@ -1938,61 +1938,61 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>阿明</t>
+          <t>星星</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>618年中庆</t>
+          <t>元旦集卡</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1006</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>海盐</t>
+          <t>浮云</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>520告白季</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -2004,39 +2004,39 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>奶茶</t>
+          <t>小鱼</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>大树</t>
+          <t>石头</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>端午打卡</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
@@ -2048,127 +2048,127 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>浮云</t>
+          <t>海盐</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>阿明</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>520告白季</t>
+          <t>元旦集卡</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>白鹿</t>
+          <t>奶茶</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>端午打卡</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>浮云</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>元旦集卡</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>柠檬茶</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>阿明</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-07</t>
         </is>
       </c>
     </row>
@@ -2180,29 +2180,29 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>奶茶</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>端午打卡</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -2212,19 +2212,19 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>U1012</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>白鹿</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -2234,29 +2234,29 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>大树</t>
+          <t>夜风</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-01-14</t>
         </is>
       </c>
     </row>
